--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6805-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6805-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52780489-C899-481B-B2F7-315761285FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B7ED22D6-5269-4A56-ADAE-80C9B0467D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{480187D3-57BB-4206-A9D2-E32E046364C0}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{0C63FB0C-2013-4D44-A77D-D7DA5AB93FFC}"/>
   </bookViews>
   <sheets>
     <sheet name="6805-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1439,30 +1439,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F88978AE-B58A-442F-BBE1-3660B0DB8854}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE6A5FF2-410B-4CB6-BC1B-E517E6F1B73C}">
   <dimension ref="A1:X11"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1532,7 +1532,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1652,7 +1652,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1724,7 +1724,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2021</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="34">
         <v>2020</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
         <v>35</v>
       </c>
